--- a/data/hsk1/excel/bai-06.xlsx
+++ b/data/hsk1/excel/bai-06.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiểm tra" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Luyện viết" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lời thoại" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Câu hỏi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bài khoá" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ngữ pháp" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ví dụ" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
@@ -3680,44 +3680,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Bài khoá</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Nhân vật</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Vai</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chữ đại diện</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tiếng Trung</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pinyin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Nghĩa tiếng Việt</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Từ nhấn</t>
         </is>
@@ -3726,30 +3738,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Lý Văn</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Sinh viên</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>家月，你的手机号是多少？</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Jiāyuè, nǐ de shǒujī hào shì duōshao?</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Gia Nguyệt, số điện thoại của bạn là bao nhiêu?</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>手机</t>
         </is>
@@ -3758,30 +3780,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Bạch Gia Nguyệt</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Sinh viên</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>我的手机号是0932463321。</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Wǒ de shǒujī hào shì líng jiǔ sān èr sì liù sān sān èr yāo.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Số điện thoại của tôi là 0932463321.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>手机</t>
         </is>
@@ -3790,78 +3822,108 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Lý Văn</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>我的手机号是0932581127。</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Wǒ de shǒujī hào shì líng jiǔ sān èr wǔ bā yāo yāo èr qī.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Số điện thoại của tôi là 0932581127.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>Bạch Gia Nguyệt</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>好的。</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Hǎo de.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Được rồi.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Trần Thiên Trung</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Sinh viên</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>陈</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>家月，明天你去哪儿？</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Jiāyuè, míngtiān nǐ qù nǎr?</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Gia Nguyệt, ngày mai bạn đi đâu?</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>哪儿</t>
         </is>
@@ -3870,26 +3932,36 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>Bạch Gia Nguyệt</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>我想去超市买东西。</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Wǒ xiǎng qù chāoshì mǎi dōngxi.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Tôi muốn đi siêu thị mua đồ.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>超市</t>
         </is>
@@ -3898,26 +3970,36 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>Trần Thiên Trung</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>陈</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>你去超市买什么？</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Nǐ qù chāoshì mǎi shénme?</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Bạn đi siêu thị mua gì?</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>买</t>
         </is>
@@ -3926,26 +4008,36 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>Bạch Gia Nguyệt</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>我想买一些牛奶。</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Wǒ xiǎng mǎi yìxiē niúnǎi.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Tôi muốn mua một ít sữa.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>牛奶</t>
         </is>
@@ -3954,30 +4046,40 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>Vương Nhất Tuyết</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Mẹ</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>星期天我们去哪儿吃晚饭？</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Xīngqītiān wǒmen qù nǎr chī wǎnfàn?</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Chủ nhật chúng ta đi đâu ăn tối?</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>晚饭</t>
         </is>
@@ -3986,30 +4088,40 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>Lưu Minh</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Bố</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>我还想去西安饭店。</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Wǒ hái xiǎng qù Xī’ān fàndiàn.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Anh vẫn muốn đi nhà hàng Tây An.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>想</t>
         </is>
@@ -4018,26 +4130,36 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>Vương Nhất Tuyết</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>那里的包子非常好吃，我想吃包子。</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Nàli de bāozi fēicháng hǎochī, wǒ xiǎng chī bāozi.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Bánh bao ở đó rất ngon, em muốn ăn bánh bao.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>好吃</t>
         </is>
@@ -4046,30 +4168,40 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>Lưu Tiểu Minh</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Con trai</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>明</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>妈妈，我想吃米饭，不想吃包子。</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Māma, wǒ xiǎng chī mǐfàn, bù xiǎng chī bāozi.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Mẹ ơi, con muốn ăn cơm, không muốn ăn bánh bao.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>米饭</t>
         </is>
@@ -4078,26 +4210,36 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>Vương Nhất Tuyết</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>好的。我们怎么去？</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Hǎo de, wǒmen zěnme qù?</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Được thôi, chúng ta đi bằng cách nào?</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>怎么</t>
         </is>
@@ -4106,26 +4248,36 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>Lưu Minh</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>坐出租车去。</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Zuò chūzūchē qù.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Đi taxi.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>出租车</t>
         </is>
@@ -4142,154 +4294,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Câu hỏi</t>
+          <t>Bài khoá</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Tên bài khoá</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Đáp án</t>
+          <t>Tình huống</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>白家月（　）想去超市。</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>现在</t>
+          <t>Xin số điện thoại</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>今天</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>明天</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Trong khuôn viên trường, Lý Văn xin số điện thoại của Bạch Gia Nguyệt.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>白家月想买（　）。</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>菜</t>
+          <t>Ngày mai đi đâu</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>牛奶</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>面条儿和牛奶</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Trong lớp học sau giờ tan học, Bạch Gia Nguyệt và Trần Thiên Trung nói chuyện đi siêu thị.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>王一雪一家人想去西安饭店（　）。</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>吃早饭</t>
+          <t>Bữa tối cuối tuần</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>吃午饭</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>吃晚饭</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>刘小明不想吃（　）。</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>米饭</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>包子</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Ở nhà, cả nhà Vương Nhất Tuyết bàn xem chủ nhật đi đâu ăn tối.</t>
         </is>
       </c>
     </row>
